--- a/XLibur.Tests/Resource/Examples/Styles/UsingPhonetics.xlsx
+++ b/XLibur.Tests/Resource/Examples/Styles/UsingPhonetics.xlsx
@@ -387,22 +387,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:1">
-      <x:c r="A1" s="0" t="s" ph="1">
+      <x:c r="A1" t="s" ph="1">
         <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Examples/Styles/UsingPhonetics.xlsx
+++ b/XLibur.Tests/Resource/Examples/Styles/UsingPhonetics.xlsx
@@ -86,12 +86,12 @@
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>

--- a/XLibur.Tests/Resource/Examples/Styles/UsingPhonetics.xlsx
+++ b/XLibur.Tests/Resource/Examples/Styles/UsingPhonetics.xlsx
@@ -45,14 +45,14 @@
   <x:fonts count="2">
     <x:font>
       <x:vertAlign val="baseline"/>
-      <x:sz val="8"/>
+      <x:sz val="11"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
-      <x:sz val="11"/>
+      <x:sz val="8"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
@@ -86,12 +86,12 @@
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="1">
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
